--- a/SGC-CKN/Excel/a69f5c3d-48a9-4665-9d68-0aa5542cfbfc_Lô_CT-02_P7-111_D800_25-03-2026.xlsx
+++ b/SGC-CKN/Excel/a69f5c3d-48a9-4665-9d68-0aa5542cfbfc_Lô_CT-02_P7-111_D800_25-03-2026.xlsx
@@ -1239,7 +1239,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.64</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-6.97</v>
@@ -1248,10 +1248,10 @@
         <v>0.55</v>
       </c>
       <c r="I11" s="5">
-        <v>3.33</v>
+        <v>6.97</v>
       </c>
       <c r="J11" s="8">
-        <v>6.05</v>
+        <v>12.67</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.64</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-6.97</v>
@@ -1730,10 +1730,10 @@
         <v>0.55</v>
       </c>
       <c r="H2" s="5">
-        <v>3.33</v>
+        <v>6.97</v>
       </c>
       <c r="I2" s="8">
-        <v>6.05</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2011,7 +2011,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.64</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-45.05</v>
@@ -2020,10 +2020,10 @@
         <v>8.68</v>
       </c>
       <c r="H12" s="39">
-        <v>41.41</v>
+        <v>45.05</v>
       </c>
       <c r="I12" s="39">
-        <v>4.77</v>
+        <v>5.19</v>
       </c>
     </row>
   </sheetData>
